--- a/hardware/BOM_PCB_基于ESP32S3的智能终端.xlsx
+++ b/hardware/BOM_PCB_基于ESP32S3的智能终端.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29328"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36D1C94D-45AB-4568-8F42-954CFC41D2B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{588A7EB3-C6AA-49DC-8502-02A96F372D3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-109" yWindow="-109" windowWidth="23452" windowHeight="12561" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,9 +17,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="103">
   <si>
-    <t>C3,C5,C6,C11,C12,C19</t>
-  </si>
-  <si>
     <t>LED1,LED2</t>
   </si>
   <si>
@@ -38,9 +35,6 @@
     <t>R14</t>
   </si>
   <si>
-    <t>R19</t>
-  </si>
-  <si>
     <t>U2</t>
   </si>
   <si>
@@ -56,9 +50,6 @@
     <t>U6</t>
   </si>
   <si>
-    <t>U7</t>
-  </si>
-  <si>
     <t>U8</t>
   </si>
   <si>
@@ -81,10 +72,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>C1,C2，C4,C7,C8,C9,C10,C15,C16,C17,C18,C20</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>C13</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -226,14 +213,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>https://item.taobao.com/item.htm?id=569513203579&amp;mi_id=0000R4XL5iDQh_0lI-eKOfrSQqLF2N_SuYQMKehYWQrutbw&amp;spm=tbpc.boughtlist.suborder_itemtitle.1.3d8f2e8dMW9QnL</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>拨动开关</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>https://item.taobao.com/item.htm?id=765348364182&amp;mi_id=0000GF14ZfPl1HE5gZAs8mX55APPlwTopy1bBQlghk8hGhY&amp;spm=tbpc.boughtlist.suborder_itemtitle.1.3d8f2e8dMW9QnL</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -274,14 +253,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>https://item.taobao.com/item.htm?id=522579028878&amp;mi_id=0000xzGTae6T5_061GJpulW2p1jD_ikLteW3q7WmcOXn0ms&amp;spm=tbpc.boughtlist.suborder_itemtitle.1.3d8f2e8dMW9QnL</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>AMS1117-3.3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>https://item.taobao.com/item.htm?id=958700013927&amp;mi_id=0000HfmFhMhqdhwYMdqnFv5-rnvj97TMAEuWCSixogPUaV0&amp;spm=tbpc.boughtlist.suborder_itemtitle.1.3d8f2e8dMW9QnL</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -303,10 +274,6 @@
   </si>
   <si>
     <t>TypeC-16P母座</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://item.taobao.com/item.htm?id=628330839231&amp;pisk=griSShwt-_fSBUgTPkJV5eyT8VrQPK-Zw9wKIvIPpuE899Gxp8I8yyBYk82C2yFerXaITj4K4ukrGWhZOJorYvBQpjr8-4PUaWZIKf92_h-ZEYq3JCRwbs_MkHqGy6URT-FYBkw-0UggrYq3vB6VvF-sEbzG9Z6Lp-pbLJVLpXF8HiF0dgC-97UAMJ23vWhK9nKYKR5dwkU8kKw_L6I8wkBYM8yF28hLvKZYCSFLvzhKHKw3MWHjBCwDW7HWIDWNojB52YNfvMnbHBVtF1jQ3meWO5M7GBvEch476YFfvQgz2JNQicd2lx0xybymOhObxj0K9JGAMBzopqGbFbR1tWooUDNrFUdohoFSwzgXBa2j30MIJr9J2xZ7NPojw97uV2hoAz05KdDY2j0gszLDi-irbyNglsd-3xN852GyiMFr5xhb7m5VbkcmJXeIM_syrGP_vdQChPjQh5JXhwbHmklkBnPMqG48n-o2hK15gze0h5JXhwb3y-24RK9fNs5..&amp;spm=a1z10.3-c-s.w4002-24706531953.29.6f0b6a4bP5ygQu&amp;skuId=4677625976670</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -406,10 +373,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>R1,R8,R11,R17,R20,R21,R22,R23,R24,R26</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>https://item.taobao.com/item.htm?id=552629356951&amp;pisk=fFBZGEZVFReahOasNFJq4Hv9IOv9_LUWItTXmijDfFYM5t_VmntvjnDDiDvHmeMbXdNv3Z8FkFO6IFM23i7AlIXXltoOLakjCPFOmxJXnza7F8sOfKp0P0outx394nK0hnYMth8jCua7F8sEtYTUYz1_7Xokan9DjFvDtk-2jhvDsIA3YnxjSEYGoMcIT1humoAu7gYh1VpXN4r1sekmU0KwsLwJ-xDcLhS6rGVxnxXebCWFJB0i8C1c2QB1A-kpCg5HK3sTQvJlj376Ra2oLpjCxZOR9rHW9wW2wOAimkYhQwW9INNmUaJNuQXMTmDfjMY9LHXucbLCLF_cQBqSUI9hFQvGOWU6Gd-PoOQZ0xbl403vx-VfH1umgCxpYUZUYGVCdyJQp77qMjdOwH87XuGxMCxpYUZUYjhv6dxePlE5.&amp;spm=a1z10.3-c-s.w4002-24706531953.10.6ac36a4bzX7DWm</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -426,10 +389,51 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>轻触开关4.5*4.5*3.8/4.3/4.8/5/6/8MM边三脚按键 侧插侧按边三角-淘宝网</t>
-  </si>
-  <si>
-    <t>4.5*4.5*8三角侧按键</t>
+    <t>C1,C2,C4,C7,C8,C9,C10,C15,C16,C17,C18,C20,C22,C24</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>C3,C5,C6,C19,C21,C23</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>R1,R8,R11,R17,R20,R21,R22,R23,R24,R25</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>R26</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>U12</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://item.taobao.com/item.htm?id=546701607083&amp;pisk=fmIIG0vArXcIJJTKuTeZlmW1Hdt7A6ZV9Y9RnTnEeHKpwY1OepnpJUH9WpvSvUdz-_T5a1YRYHWF1QCVNLSF4THWe1-prwRyTQt5EswagorVK9xkySP40Zb5aixmy2L-aCE9Kb2CnrrVK9Ak3NYL5orSXihoPLCJJCB9nCp-ppCJXFpv6Dp-v3dTCLcBfcntibXTwcnso09Qkio-IAj6B7AAdUJMQGTHJILB60BNfpTBM9Ixoj5XBGS6uFkzNhBc76p6clupDO_RGZCuuVxCewCk56Vi5C7OxTdJ7YnfCt6dkhIzexY16LTv2FM-2OtH6_seDoh6INBFyMfIF0phYi8WiFw-qU-O0EQAOY2cBHpR4Oo2G3exPATmVdO4CRgorBol68rwikmDJdvNbRwsOf8pIdO4CRgorepMQUw_CXGN.&amp;spm=a1z10.3-c-s.w4002-24706531953.10.7ae16a4bexYB52</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RT9013-33GB</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://item.taobao.com/item.htm?app=chrome&amp;bxsign=scdsmyQfraEYU_ygaGT5pE_JGXBUebF0W3HmYPx5XMJTn9E0GsWW9imLMd6ne1gr3wHib65-uiB7Qt1N6yMRX2znmfDmnlpFpE7fCb-o5NxXOa5eFAmoZ-2-CRqil4M1Gb5ppli1Tqb-jCZnSbj8ASDmw&amp;cpp=1&amp;h5_spm=a-tb-item.b-tb-item&amp;id=930710071419&amp;share_crt_v=1&amp;shareurl=true&amp;short_name=h.70k7IQhOPkJQQqV&amp;skuId=5983626110298&amp;sp_tk=S29JWWZydmtkWTA%3D&amp;spm=a2159r.13376460.0.0&amp;tbSocialPopKey=shareItem&amp;tk=KoIYfrvkdY0&amp;un=1bf58bd13a34bacd745a32f3a3258754&amp;un_site=0&amp;ut_sk=1.aRnRmspHGbYDANllt4%2FPVnfC_21380790_1765099361535.TaoPassword-Weixin.1&amp;wxsign=tbw5g9Z9Fgmg3mf9BOR1n11w6WhAwLPhOkLBHELs82xsaeYP8y1pd-uAeLSmo4pcn8haL8_M-GWOmVUfeO-MRLy18GQAww8u9M4ubhB7nJCA1FTrt-8Pr5Pxa8QnuVDDwzIvFjB7DdbJNYlFhSo8cC2Hg&amp;x-ssr=true</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://item.taobao.com/item.htm?app=chrome&amp;bxsign=scd2MHxb-Ym1uDdD4XMdHdumIKW0UuGni3zaEQnHyiMJi5pFAVleOVhz4VsD_7BqGXRITvn25AKF2meaYdkGBysleAF0gndKOJSO0Dabq2-LlilseqxaOkUz-caJeezM4aR6KT1m9Q8OM_wX7ENG12Www&amp;cpp=1&amp;h5_spm=a-tb-item.b-tb-item&amp;id=617878326279&amp;share_crt_v=1&amp;shareurl=true&amp;short_name=h.70tasX9uuMABCLN&amp;sp_tk=V0IwM2ZydmtqZ0o%3D&amp;spm=a2159r.13376460.0.0&amp;tbSocialPopKey=shareItem&amp;tk=WB03frvkjgJ&amp;un=1bf58bd13a34bacd745a32f3a3258754&amp;un_site=0&amp;ut_sk=1.aRnRmspHGbYDANllt4%2FPVnfC_21380790_1765099361535.TaoPassword-Weixin.1&amp;wxsign=tbwnFifgUGwAyBmp6_dXclySK8mrWKRVaNZCtqY_M-_HgFwh8O0LKJW9UEbma86wvG7zeXp2ddLq9yLNhQvv187mmuGMZJsP_iaYYZ7kxIOkFT3nscmW4WKZ9tiKTxM0NmxAjlzmRHAM9fJbc0mMpRolg&amp;x-ssr=true&amp;sku_properties=1627207%3A116371684</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>轻触开关6*6*7.0H</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://item.taobao.com/item.htm?app=chrome&amp;bxsign=scdDrWDFaYZZvx2uZdw9dUrl05o8tGt1F-zwKdUV70aS9zX4mftB4fYqF9FJyoUd-hZn4EYZXShmVZQGyHKXPogzNUheZ-CSm4dQpqon3ccrDbosXS9LPQXwQHNtTw7YxjYTTPi2SIM-BbZGFCIq4K5aA&amp;cpp=1&amp;h5_spm=a-tb-item.b-tb-item&amp;id=703408495379&amp;share_crt_v=1&amp;shareurl=true&amp;short_name=h.7boSP5LOau3wY1D&amp;sp_tk=RTVjN2Zydmt3Y1c%3D&amp;spm=a2159r.13376460.0.0&amp;tbSocialPopKey=shareItem&amp;tk=E5c7frvkwcW&amp;un=1bf58bd13a34bacd745a32f3a3258754&amp;un_site=0&amp;ut_sk=1.aRnRmspHGbYDANllt4%2FPVnfC_21380790_1765099361535.TaoPassword-Weixin.1&amp;wxsign=tbwtPXZScjSrhkfBYJNHVEz3g1AVxhIpsjbRqJc3TMfS2TTOp7tcf9WBo3v25lMpbvnY3wzPu_e1e0fITicsOlwKaSCNWFkPx_wVEXscfLpIZ5Z1Wg4tbVwWYVfS9qAAo7pueh4Z0cCtCJWCnvPhcdMBw&amp;x-ssr=true</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>拨动开关柄高4H</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -844,417 +848,417 @@
   <dimension ref="A1:C37"/>
   <sheetFormatPr defaultRowHeight="14.55" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="46.6640625" customWidth="1"/>
-    <col min="2" max="2" width="40.88671875" customWidth="1"/>
+    <col min="1" max="1" width="53.21875" customWidth="1"/>
+    <col min="2" max="2" width="41" customWidth="1"/>
     <col min="3" max="3" width="46.88671875" customWidth="1"/>
     <col min="4" max="4" width="20" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" t="s">
         <v>20</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C3" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C5" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C8" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B9" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C9" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="C10" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="C11" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B12" t="s">
-        <v>77</v>
+        <v>98</v>
       </c>
       <c r="C12" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C13" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C14" t="s">
         <v>47</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C14" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C15" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C16" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="15.15" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="C17" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="C18" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C19" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C20" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C21" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="C22" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="15.15" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="C23" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>7</v>
+        <v>94</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="C24" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>57</v>
+        <v>101</v>
       </c>
       <c r="C25" t="s">
-        <v>58</v>
+        <v>102</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="C26" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B27" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="C27" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="C28" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="C29" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="C30" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>69</v>
+        <v>96</v>
       </c>
       <c r="C31" t="s">
-        <v>70</v>
+        <v>97</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>13</v>
+        <v>95</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="C32" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="C33" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="C34" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="C35" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="C36" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="C37" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
     </row>
   </sheetData>
@@ -1271,12 +1275,12 @@
     <hyperlink ref="B15" r:id="rId9" xr:uid="{DA08EDF0-9928-451F-91AE-AA3B3561B5FA}"/>
     <hyperlink ref="B14" r:id="rId10" xr:uid="{4D762C97-F9F3-41D5-AFA5-272A7A7C9FD5}"/>
     <hyperlink ref="B16" r:id="rId11" xr:uid="{0B49417B-4DBF-4994-95E0-EA43AA5E7B3E}"/>
-    <hyperlink ref="B25" r:id="rId12" xr:uid="{F2B17918-F1CD-4A3F-8ED9-20ACA8F823E2}"/>
+    <hyperlink ref="B25" r:id="rId12" display="https://item.taobao.com/item.htm?id=569513203579&amp;mi_id=0000R4XL5iDQh_0lI-eKOfrSQqLF2N_SuYQMKehYWQrutbw&amp;spm=tbpc.boughtlist.suborder_itemtitle.1.3d8f2e8dMW9QnL" xr:uid="{F2B17918-F1CD-4A3F-8ED9-20ACA8F823E2}"/>
     <hyperlink ref="B26" r:id="rId13" xr:uid="{A649C5BF-C17C-4198-B2B7-96EA8D21B718}"/>
     <hyperlink ref="B28" r:id="rId14" xr:uid="{19D1A1AE-F435-477D-8E69-4598E680D90B}"/>
     <hyperlink ref="B29" r:id="rId15" xr:uid="{2457B954-BCC2-4063-B59A-B4686787F27D}"/>
     <hyperlink ref="B30" r:id="rId16" xr:uid="{78A56D3C-9934-4BED-BB68-683649A21603}"/>
-    <hyperlink ref="B31" r:id="rId17" xr:uid="{4399402F-AC4A-44B8-8F24-C0E63462FFE4}"/>
+    <hyperlink ref="B31" r:id="rId17" display="https://item.taobao.com/item.htm?id=546701607083&amp;pisk=fmIIG0vArXcIJJTKuTeZlmW1Hdt7A6ZV9Y9RnTnEeHKpwY1OepnpJUH9WpvSvUdz-_T5a1YRYHWF1QCVNLSF4THWe1-prwRyTQt5EswagorVK9xkySP40Zb5aixmy2L-aCE9Kb2CnrrVK9Ak3NYL5orSXihoPLCJJCB9nCp-ppCJXFpv6Dp-v3dTCLcBfcntibXTwcnso09Qkio-IAj6B7AAdUJMQGTHJILB60BNfpTBM9Ixoj5XBGS6uFkzNhBc76p6clupDO_RGZCuuVxCewCk56Vi5C7OxTdJ7YnfCt6dkhIzexY16LTv2FM-2OtH6_seDoh6INBFyMfIF0phYi8WiFw-qU-O0EQAOY2cBHpR4Oo2G3exPATmVdO4CRgorBol68rwikmDJdvNbRwsOf8pIdO4CRgorepMQUw_CXGN.&amp;spm=a1z10.3-c-s.w4002-24706531953.10.7ae16a4bexYB52" xr:uid="{4399402F-AC4A-44B8-8F24-C0E63462FFE4}"/>
     <hyperlink ref="B32" r:id="rId18" xr:uid="{ECA04BE2-1916-405F-8354-A6345AE29F9C}"/>
     <hyperlink ref="B33" r:id="rId19" xr:uid="{A458F1A6-1F58-40DF-B405-89202C010D84}"/>
     <hyperlink ref="B35" r:id="rId20" xr:uid="{CDDC7513-93F0-411F-9514-4D13DBEC2629}"/>
